--- a/data/scuc-tea-5yr-snapshot-df.xlsx
+++ b/data/scuc-tea-5yr-snapshot-df.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/D/Library/Mobile Documents/com~apple~CloudDocs/R Working Directory/scuc-data-analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/D/Library/Mobile Documents/com~apple~CloudDocs/R Working Directory/scuc-data-analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6490D73-B499-1C4A-A6A0-684B057B8CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D0C7DA-E4FA-A941-82D6-944AA885C12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="32000" windowHeight="18000" xr2:uid="{571C89DC-EB47-ED4A-B998-17E5B079E322}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="32000" windowHeight="17500" xr2:uid="{571C89DC-EB47-ED4A-B998-17E5B079E322}"/>
   </bookViews>
   <sheets>
-    <sheet name="tea snapshots 2017-2021" sheetId="2" r:id="rId1"/>
+    <sheet name="tea snapshots 2017-2021 " sheetId="2" r:id="rId1"/>
     <sheet name="Op Exp per Pupil 2017-21   XmR " sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="141">
   <si>
     <t>Year</t>
   </si>
@@ -384,9 +384,6 @@
     <t>Approach_Writing</t>
   </si>
   <si>
-    <t>Approach_Math</t>
-  </si>
-  <si>
     <t>Approach_Science</t>
   </si>
   <si>
@@ -402,9 +399,6 @@
     <t>Mts_Writing</t>
   </si>
   <si>
-    <t>Mts_Math</t>
-  </si>
-  <si>
     <t>Mts_Science</t>
   </si>
   <si>
@@ -420,9 +414,6 @@
     <t>Masters_Writing</t>
   </si>
   <si>
-    <t>Masters_Math</t>
-  </si>
-  <si>
     <t>Masters_Science</t>
   </si>
   <si>
@@ -460,6 +451,18 @@
   </si>
   <si>
     <t>LCL</t>
+  </si>
+  <si>
+    <t>All_Grades_Approach_Math</t>
+  </si>
+  <si>
+    <t>All-Grades_Mts_Math</t>
+  </si>
+  <si>
+    <t>All_Grades_Masters_Math</t>
+  </si>
+  <si>
+    <t>*  THESE ARE DISTRICT-WIDE NUMBERS COVERING ALL GRADE LEVELS</t>
   </si>
 </sst>
 </file>
@@ -468,11 +471,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -492,6 +495,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -501,12 +511,49 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -515,7 +562,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -532,16 +579,16 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -553,7 +600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -563,16 +610,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -587,11 +634,16 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3429,7 +3481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6002E3-2608-DF4C-8A24-B2CCC82DE01D}">
-  <dimension ref="A1:DZ6"/>
+  <dimension ref="A1:DZ10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="16"/>
@@ -3730,7 +3782,7 @@
         <v>90</v>
       </c>
       <c r="CN1" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="CO1" s="2" t="s">
         <v>91</v>
@@ -3802,49 +3854,49 @@
         <v>113</v>
       </c>
       <c r="DL1" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="DM1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="DM1" s="2" t="s">
+      <c r="DN1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="DN1" s="2" t="s">
+      <c r="DO1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="DO1" s="2" t="s">
+      <c r="DP1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="DP1" s="2" t="s">
+      <c r="DQ1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="DQ1" s="2" t="s">
+      <c r="DR1" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="DS1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="DR1" s="2" t="s">
+      <c r="DT1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="DS1" s="2" t="s">
+      <c r="DU1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="DT1" s="2" t="s">
+      <c r="DV1" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="DU1" s="2" t="s">
+      <c r="DW1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="DV1" s="2" t="s">
+      <c r="DX1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="DY1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="DW1" s="2" t="s">
+      <c r="DZ1" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="DX1" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="DY1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="DZ1" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:130" ht="20" x14ac:dyDescent="0.25">
@@ -3927,7 +3979,7 @@
         <v>9818</v>
       </c>
       <c r="AA2" s="23" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AB2" s="5">
         <v>0.43</v>
@@ -3939,7 +3991,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="AE2" s="24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AF2" s="6">
         <v>0.20399999999999999</v>
@@ -3966,13 +4018,13 @@
         <v>2.7E-2</v>
       </c>
       <c r="AN2" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AO2" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AP2" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AQ2" s="6">
         <v>0.72199999999999998</v>
@@ -4200,7 +4252,7 @@
         <v>0.86</v>
       </c>
       <c r="DN2" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DO2" s="11">
         <v>0.57999999999999996</v>
@@ -4218,7 +4270,7 @@
         <v>0.61</v>
       </c>
       <c r="DT2" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DU2" s="11">
         <v>0.27</v>
@@ -4236,7 +4288,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="DZ2" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:130" ht="20" x14ac:dyDescent="0.25">
@@ -4358,13 +4410,13 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="AN3" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AO3" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AP3" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AQ3" s="6">
         <v>0.68300000000000005</v>
@@ -4592,7 +4644,7 @@
         <v>0.87</v>
       </c>
       <c r="DN3" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DO3" s="11">
         <v>0.57999999999999996</v>
@@ -4610,7 +4662,7 @@
         <v>0.63</v>
       </c>
       <c r="DT3" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DU3" s="11">
         <v>0.28000000000000003</v>
@@ -4628,7 +4680,7 @@
         <v>0.31</v>
       </c>
       <c r="DZ3" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:130" ht="20" x14ac:dyDescent="0.25">
@@ -4897,130 +4949,130 @@
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="CK4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CL4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CM4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CN4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CO4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CP4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CQ4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CR4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CS4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CT4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CU4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CV4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CW4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CX4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CY4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="CZ4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DA4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DB4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DC4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DD4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DE4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DF4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DG4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DH4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DI4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DJ4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DK4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DL4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DM4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DN4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DO4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DP4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DQ4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DR4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DS4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DT4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DU4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DV4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DW4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DX4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DY4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="DZ4" s="12" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:130" x14ac:dyDescent="0.25">
@@ -5806,6 +5858,18 @@
       <c r="DZ6" s="11">
         <v>0.39</v>
       </c>
+    </row>
+    <row r="9" spans="1:130" ht="20" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:130" ht="25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5833,94 +5897,94 @@
         <v>4</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>139</v>
-      </c>
       <c r="J1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="M1" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="P1" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="R1" s="16" t="s">
         <v>136</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25">
+      <c r="A2" s="15">
         <v>2017</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="16">
         <v>8099</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="16">
         <f t="shared" ref="C2:C26" ca="1" si="0">F2+2.66*O2</f>
         <v>9034.9650000000001</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="16">
         <f t="shared" ref="D2:D26" ca="1" si="1">F2+(2/3)*2.66*O2</f>
         <v>8844.11</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="16">
         <f t="shared" ref="E2:E26" ca="1" si="2">F2+(1/3)*2.66*O2</f>
         <v>8653.2549999999992</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="16">
         <f t="shared" ref="F2:F26" si="3">AVERAGE($B$2:$B$6)</f>
         <v>8462.4</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="16">
         <f t="shared" ref="G2:G26" ca="1" si="4">F2-(1/3)*2.66*O2</f>
         <v>8271.5450000000001</v>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="16">
         <f t="shared" ref="H2:H26" ca="1" si="5">F2-(2/3)*2.66*O2</f>
         <v>8080.69</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="16">
         <f t="shared" ref="I2:I26" ca="1" si="6">F2-2.66*O2</f>
         <v>7889.8349999999991</v>
       </c>
-      <c r="J2" s="26">
+      <c r="J2" s="16">
         <f>B2</f>
         <v>8099</v>
       </c>
-      <c r="K2" s="26"/>
+      <c r="K2" s="16"/>
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
       <c r="N2" s="16"/>
@@ -5933,45 +5997,45 @@
       <c r="R2" s="16"/>
     </row>
     <row r="3" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25">
+      <c r="A3" s="15">
         <v>2018</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="16">
         <v>8258</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>9034.9650000000001</v>
       </c>
-      <c r="D3" s="26">
+      <c r="D3" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>8844.11</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>8653.2549999999992</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="16">
         <f t="shared" si="3"/>
         <v>8462.4</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="16">
         <f t="shared" ca="1" si="4"/>
         <v>8271.5450000000001</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="16">
         <f t="shared" ca="1" si="5"/>
         <v>8080.69</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="16">
         <f t="shared" ca="1" si="6"/>
         <v>7889.8349999999991</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3">
         <f t="shared" ref="J3:J26" ca="1" si="8">IF(ISBLANK(B3),OFFSET(J3,-1,0,1,1),B3)</f>
         <v>8258</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="16">
         <f t="shared" ref="K3:K26" ca="1" si="9">IF(OR(OFFSET(K3,-1,-9,1,1)="",OFFSET(K3,0,-9,1,1)=""),"",IF(ISERROR(ABS(B3-OFFSET(K3,-1,-1,1,1))),"",ABS(B3-OFFSET(K3,-1,-1,1,1))))</f>
         <v>159</v>
       </c>
@@ -6004,45 +6068,45 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25">
+      <c r="A4" s="15">
         <v>2019</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="16">
         <v>8358</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>9034.9650000000001</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>8844.11</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>8653.2549999999992</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="16">
         <f t="shared" si="3"/>
         <v>8462.4</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="16">
         <f t="shared" ca="1" si="4"/>
         <v>8271.5450000000001</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="16">
         <f t="shared" ca="1" si="5"/>
         <v>8080.69</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="16">
         <f t="shared" ca="1" si="6"/>
         <v>7889.8349999999991</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4">
         <f t="shared" ca="1" si="8"/>
         <v>8358</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="16">
         <f t="shared" ca="1" si="9"/>
         <v>100</v>
       </c>
@@ -6075,45 +6139,45 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="25">
+      <c r="A5" s="15">
         <v>2020</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="16">
         <v>8637</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>9034.9650000000001</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>8844.11</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>8653.2549999999992</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="16">
         <f t="shared" si="3"/>
         <v>8462.4</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="16">
         <f t="shared" ca="1" si="4"/>
         <v>8271.5450000000001</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="16">
         <f t="shared" ca="1" si="5"/>
         <v>8080.69</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="16">
         <f t="shared" ca="1" si="6"/>
         <v>7889.8349999999991</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5">
         <f t="shared" ca="1" si="8"/>
         <v>8637</v>
       </c>
-      <c r="K5" s="26">
+      <c r="K5" s="16">
         <f t="shared" ca="1" si="9"/>
         <v>279</v>
       </c>
@@ -6146,45 +6210,45 @@
       </c>
     </row>
     <row r="6" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25">
+      <c r="A6" s="15">
         <v>2021</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="16">
         <v>8960</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="16">
         <f t="shared" ca="1" si="0"/>
         <v>9034.9650000000001</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="16">
         <f t="shared" ca="1" si="1"/>
         <v>8844.11</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="16">
         <f t="shared" ca="1" si="2"/>
         <v>8653.2549999999992</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="16">
         <f t="shared" si="3"/>
         <v>8462.4</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="16">
         <f t="shared" ca="1" si="4"/>
         <v>8271.5450000000001</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="16">
         <f t="shared" ca="1" si="5"/>
         <v>8080.69</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="16">
         <f t="shared" ca="1" si="6"/>
         <v>7889.8349999999991</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6">
         <f t="shared" ca="1" si="8"/>
         <v>8960</v>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="16">
         <f t="shared" ca="1" si="9"/>
         <v>323</v>
       </c>
